--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/95.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/95.xlsx
@@ -426,13 +426,13 @@
         <v>-4.886289993826119</v>
       </c>
       <c r="E2">
-        <v>-11.59987391478954</v>
+        <v>-11.16653518004754</v>
       </c>
       <c r="F2">
-        <v>-2.465936419047452</v>
+        <v>-2.545875530152411</v>
       </c>
       <c r="G2">
-        <v>-8.500541463494201</v>
+        <v>-8.828509402025379</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-4.809409380996063</v>
       </c>
       <c r="E3">
-        <v>-12.3162241611149</v>
+        <v>-13.19471641928489</v>
       </c>
       <c r="F3">
-        <v>-2.233470846432424</v>
+        <v>-2.375506034786039</v>
       </c>
       <c r="G3">
-        <v>-8.369220414242104</v>
+        <v>-9.018990875994263</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-4.890961010216918</v>
       </c>
       <c r="E4">
-        <v>-13.14549190682151</v>
+        <v>-13.09970903460397</v>
       </c>
       <c r="F4">
-        <v>-2.142727339292752</v>
+        <v>-2.532103093713466</v>
       </c>
       <c r="G4">
-        <v>-9.213731375547308</v>
+        <v>-9.075890539056594</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-5.117287195232068</v>
       </c>
       <c r="E5">
-        <v>-13.08389107489517</v>
+        <v>-14.71965739899785</v>
       </c>
       <c r="F5">
-        <v>-2.180162918960068</v>
+        <v>-1.874236068329974</v>
       </c>
       <c r="G5">
-        <v>-8.674616829665862</v>
+        <v>-9.299765004835947</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-5.448256499195425</v>
       </c>
       <c r="E6">
-        <v>-13.68921672397448</v>
+        <v>-14.57227368394421</v>
       </c>
       <c r="F6">
-        <v>-2.048952835826237</v>
+        <v>-2.197791405659044</v>
       </c>
       <c r="G6">
-        <v>-9.196111215773088</v>
+        <v>-9.054457599830302</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-5.832115412972768</v>
       </c>
       <c r="E7">
-        <v>-15.19507471421911</v>
+        <v>-15.19497055931693</v>
       </c>
       <c r="F7">
-        <v>-1.538064695456267</v>
+        <v>-1.867031757027827</v>
       </c>
       <c r="G7">
-        <v>-9.403609104749254</v>
+        <v>-8.731687116249285</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-6.20617659728938</v>
       </c>
       <c r="E8">
-        <v>-15.63831269314187</v>
+        <v>-16.20188128339645</v>
       </c>
       <c r="F8">
-        <v>-1.376673046001437</v>
+        <v>-1.362332349524172</v>
       </c>
       <c r="G8">
-        <v>-9.652017264128576</v>
+        <v>-9.944685821123247</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-6.505666449458892</v>
       </c>
       <c r="E9">
-        <v>-16.35995219710819</v>
+        <v>-16.34082392289979</v>
       </c>
       <c r="F9">
-        <v>-1.190805624896089</v>
+        <v>-1.275492109586491</v>
       </c>
       <c r="G9">
-        <v>-9.080257844952214</v>
+        <v>-9.808846529783795</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-6.668232531546471</v>
       </c>
       <c r="E10">
-        <v>-16.55163344490486</v>
+        <v>-16.91544651820709</v>
       </c>
       <c r="F10">
-        <v>-1.271625290550223</v>
+        <v>-1.012313987145269</v>
       </c>
       <c r="G10">
-        <v>-9.308338836770776</v>
+        <v>-9.958680231074279</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-6.639700702547067</v>
       </c>
       <c r="E11">
-        <v>-17.84687663752675</v>
+        <v>-19.34534415819086</v>
       </c>
       <c r="F11">
-        <v>-0.3860036179714242</v>
+        <v>-0.355851872876925</v>
       </c>
       <c r="G11">
-        <v>-9.486102295975254</v>
+        <v>-9.119812970851321</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-6.387901048305814</v>
       </c>
       <c r="E12">
-        <v>-18.46547524392254</v>
+        <v>-18.18754920864978</v>
       </c>
       <c r="F12">
-        <v>-0.3645431036670974</v>
+        <v>-0.7704406459366467</v>
       </c>
       <c r="G12">
-        <v>-9.257693182000747</v>
+        <v>-9.698695922033236</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-5.895408656215396</v>
       </c>
       <c r="E13">
-        <v>-18.12617480042383</v>
+        <v>-18.65710215003111</v>
       </c>
       <c r="F13">
-        <v>-0.2689503337514372</v>
+        <v>0.1302100964311437</v>
       </c>
       <c r="G13">
-        <v>-9.727767545049916</v>
+        <v>-8.020334688269466</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-5.17738981260738</v>
       </c>
       <c r="E14">
-        <v>-18.85741466928641</v>
+        <v>-19.04493877794403</v>
       </c>
       <c r="F14">
-        <v>0.1327150794572095</v>
+        <v>0.4656715584406511</v>
       </c>
       <c r="G14">
-        <v>-8.606649606283524</v>
+        <v>-8.853942150332635</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-4.268792090379804</v>
       </c>
       <c r="E15">
-        <v>-19.81160942744263</v>
+        <v>-19.12039221185984</v>
       </c>
       <c r="F15">
-        <v>0.3371288183438351</v>
+        <v>0.6895627000693015</v>
       </c>
       <c r="G15">
-        <v>-8.408929757554505</v>
+        <v>-9.496589080079239</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-3.223063185905223</v>
       </c>
       <c r="E16">
-        <v>-19.47705482470396</v>
+        <v>-20.51496295336597</v>
       </c>
       <c r="F16">
-        <v>0.6897449408979174</v>
+        <v>0.6995602662536887</v>
       </c>
       <c r="G16">
-        <v>-8.168534341223348</v>
+        <v>-9.112213661719647</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-2.109752337042482</v>
       </c>
       <c r="E17">
-        <v>-21.53791806085466</v>
+        <v>-21.66471080459542</v>
       </c>
       <c r="F17">
-        <v>1.105008005023518</v>
+        <v>0.9004343912281521</v>
       </c>
       <c r="G17">
-        <v>-7.245667809078604</v>
+        <v>-7.18831533744107</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-0.9896253891868976</v>
       </c>
       <c r="E18">
-        <v>-21.90966502061833</v>
+        <v>-22.22364676594015</v>
       </c>
       <c r="F18">
-        <v>1.22517263720842</v>
+        <v>1.055751622518254</v>
       </c>
       <c r="G18">
-        <v>-6.455093567767554</v>
+        <v>-7.120449831927075</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>0.07395956367576849</v>
       </c>
       <c r="E19">
-        <v>-22.43201996892909</v>
+        <v>-23.65209049302366</v>
       </c>
       <c r="F19">
-        <v>1.559982174071924</v>
+        <v>1.16055169611603</v>
       </c>
       <c r="G19">
-        <v>-5.940729276109001</v>
+        <v>-5.63865673812496</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>1.040924138709551</v>
       </c>
       <c r="E20">
-        <v>-23.49120286847914</v>
+        <v>-23.39461957484355</v>
       </c>
       <c r="F20">
-        <v>1.843200989089075</v>
+        <v>1.713703969744234</v>
       </c>
       <c r="G20">
-        <v>-5.082853899392179</v>
+        <v>-5.074280067457351</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>1.88150615172431</v>
       </c>
       <c r="E21">
-        <v>-24.27188461655747</v>
+        <v>-26.1182747952309</v>
       </c>
       <c r="F21">
-        <v>2.246806438755078</v>
+        <v>1.206941927407608</v>
       </c>
       <c r="G21">
-        <v>-4.608208794710705</v>
+        <v>-5.350860795146064</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>2.578997721604133</v>
       </c>
       <c r="E22">
-        <v>-24.72028505584897</v>
+        <v>-25.1372307146832</v>
       </c>
       <c r="F22">
-        <v>2.31238662929991</v>
+        <v>1.929715680637455</v>
       </c>
       <c r="G22">
-        <v>-4.375284719870402</v>
+        <v>-3.525500835519172</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>3.128919232074918</v>
       </c>
       <c r="E23">
-        <v>-26.03304891440654</v>
+        <v>-25.85948609111456</v>
       </c>
       <c r="F23">
-        <v>1.918893888887283</v>
+        <v>1.92043465225649</v>
       </c>
       <c r="G23">
-        <v>-3.517458561476973</v>
+        <v>-3.472587856651566</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>3.522818023791745</v>
       </c>
       <c r="E24">
-        <v>-25.83505497384317</v>
+        <v>-26.52129539649154</v>
       </c>
       <c r="F24">
-        <v>2.523282343113441</v>
+        <v>1.923287549591731</v>
       </c>
       <c r="G24">
-        <v>-2.898935172635406</v>
+        <v>-3.503608525274557</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>3.762052009429785</v>
       </c>
       <c r="E25">
-        <v>-26.10583507713183</v>
+        <v>-26.68878100766522</v>
       </c>
       <c r="F25">
-        <v>1.886410289553903</v>
+        <v>1.556314163212328</v>
       </c>
       <c r="G25">
-        <v>-3.298564990024857</v>
+        <v>-3.157987614753567</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>3.843749960143342</v>
       </c>
       <c r="E26">
-        <v>-26.65553295150091</v>
+        <v>-25.97997067056263</v>
       </c>
       <c r="F26">
-        <v>2.306700715447094</v>
+        <v>2.140622991594626</v>
       </c>
       <c r="G26">
-        <v>-2.824671285080494</v>
+        <v>-3.737700714990021</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>3.778679282300413</v>
       </c>
       <c r="E27">
-        <v>-27.77108176702443</v>
+        <v>-27.88795715268839</v>
       </c>
       <c r="F27">
-        <v>1.815934447658526</v>
+        <v>1.319810299508652</v>
       </c>
       <c r="G27">
-        <v>-2.232794696523178</v>
+        <v>-3.409913243644613</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>3.585967458815058</v>
       </c>
       <c r="E28">
-        <v>-26.68757190510517</v>
+        <v>-26.47623708011522</v>
       </c>
       <c r="F28">
-        <v>1.579387508849905</v>
+        <v>1.275396552840154</v>
       </c>
       <c r="G28">
-        <v>-2.468363435940392</v>
+        <v>-3.403130958681241</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>3.293313024688066</v>
       </c>
       <c r="E29">
-        <v>-27.00253180081265</v>
+        <v>-28.23069923643293</v>
       </c>
       <c r="F29">
-        <v>2.045774923974083</v>
+        <v>1.540691153995529</v>
       </c>
       <c r="G29">
-        <v>-2.741154352727948</v>
+        <v>-4.174546147306693</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>2.929482742604728</v>
       </c>
       <c r="E30">
-        <v>-26.41785146473432</v>
+        <v>-26.39470190560711</v>
       </c>
       <c r="F30">
-        <v>1.777725172836996</v>
+        <v>1.482337640672721</v>
       </c>
       <c r="G30">
-        <v>-2.724452934990374</v>
+        <v>-3.056371464279123</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>2.518346731914798</v>
       </c>
       <c r="E31">
-        <v>-26.9226178199993</v>
+        <v>-26.34266521078497</v>
       </c>
       <c r="F31">
-        <v>1.863187837783821</v>
+        <v>1.211004241150937</v>
       </c>
       <c r="G31">
-        <v>-2.660183648305531</v>
+        <v>-3.137804820941422</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>2.075044111791714</v>
       </c>
       <c r="E32">
-        <v>-27.00275822451304</v>
+        <v>-26.14120245913173</v>
       </c>
       <c r="F32">
-        <v>1.58245743844468</v>
+        <v>1.182120726550124</v>
       </c>
       <c r="G32">
-        <v>-3.799148151133742</v>
+        <v>-3.396237112184847</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>1.609689170491926</v>
       </c>
       <c r="E33">
-        <v>-26.74170528339286</v>
+        <v>-26.75924859169858</v>
       </c>
       <c r="F33">
-        <v>1.788800445012426</v>
+        <v>1.577541906276468</v>
       </c>
       <c r="G33">
-        <v>-3.135317654999363</v>
+        <v>-4.273908098569798</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>1.131114673671638</v>
       </c>
       <c r="E34">
-        <v>-26.27944318516388</v>
+        <v>-25.01609856345202</v>
       </c>
       <c r="F34">
-        <v>1.616720370959273</v>
+        <v>1.392106892955382</v>
       </c>
       <c r="G34">
-        <v>-3.219704111065162</v>
+        <v>-4.657932426222529</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>0.6411701449899075</v>
       </c>
       <c r="E35">
-        <v>-26.30347126824858</v>
+        <v>-25.39735079015779</v>
       </c>
       <c r="F35">
-        <v>1.62904647791293</v>
+        <v>1.452745043575111</v>
       </c>
       <c r="G35">
-        <v>-3.506627249109246</v>
+        <v>-4.953393302764288</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>0.1480956327660839</v>
       </c>
       <c r="E36">
-        <v>-25.96442894776831</v>
+        <v>-25.65307371737093</v>
       </c>
       <c r="F36">
-        <v>1.866458232290074</v>
+        <v>1.690237977957729</v>
       </c>
       <c r="G36">
-        <v>-3.658984209778942</v>
+        <v>-4.645289879553989</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-0.3505966974173441</v>
       </c>
       <c r="E37">
-        <v>-25.30870591145764</v>
+        <v>-26.33748463652019</v>
       </c>
       <c r="F37">
-        <v>1.840656244427675</v>
+        <v>1.584311324692145</v>
       </c>
       <c r="G37">
-        <v>-4.126295784275059</v>
+        <v>-4.920807491457443</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-0.8525595645692154</v>
       </c>
       <c r="E38">
-        <v>-24.97573627462166</v>
+        <v>-25.86561764492094</v>
       </c>
       <c r="F38">
-        <v>1.878688248625006</v>
+        <v>1.784140050004276</v>
       </c>
       <c r="G38">
-        <v>-3.84980364956845</v>
+        <v>-4.268835330038897</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-1.359584933393403</v>
       </c>
       <c r="E39">
-        <v>-24.57012991470264</v>
+        <v>-23.79760847678613</v>
       </c>
       <c r="F39">
-        <v>1.925951579159134</v>
+        <v>1.627494117400084</v>
       </c>
       <c r="G39">
-        <v>-4.497815376564747</v>
+        <v>-4.057616535814321</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-1.874892425898241</v>
       </c>
       <c r="E40">
-        <v>-24.0979731007669</v>
+        <v>-24.10196721484166</v>
       </c>
       <c r="F40">
-        <v>2.042618844169417</v>
+        <v>1.776717878075192</v>
       </c>
       <c r="G40">
-        <v>-4.34741074272292</v>
+        <v>-4.852932142278769</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-2.392794757646349</v>
       </c>
       <c r="E41">
-        <v>-23.6848811733132</v>
+        <v>-23.31433425916156</v>
       </c>
       <c r="F41">
-        <v>2.339164433962806</v>
+        <v>1.927141114749555</v>
       </c>
       <c r="G41">
-        <v>-4.344651235391426</v>
+        <v>-4.563400433094928</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-2.91323650771983</v>
       </c>
       <c r="E42">
-        <v>-23.15206545004471</v>
+        <v>-23.91350571206444</v>
       </c>
       <c r="F42">
-        <v>2.223897109863255</v>
+        <v>2.177664268378209</v>
       </c>
       <c r="G42">
-        <v>-4.317082411848972</v>
+        <v>-4.264116933436415</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-3.42295956732506</v>
       </c>
       <c r="E43">
-        <v>-23.22724717552006</v>
+        <v>-22.99770788501926</v>
       </c>
       <c r="F43">
-        <v>2.030683726629881</v>
+        <v>1.732787897969929</v>
       </c>
       <c r="G43">
-        <v>-3.908222518212804</v>
+        <v>-5.60125737479041</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-3.909769840310354</v>
       </c>
       <c r="E44">
-        <v>-23.01139293347044</v>
+        <v>-22.90964265099209</v>
       </c>
       <c r="F44">
-        <v>2.026376216135324</v>
+        <v>1.673982096045192</v>
       </c>
       <c r="G44">
-        <v>-4.044813209289368</v>
+        <v>-4.546393861752326</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-4.357597560911747</v>
       </c>
       <c r="E45">
-        <v>-22.52645676588505</v>
+        <v>-21.37022866835062</v>
       </c>
       <c r="F45">
-        <v>2.348584628067442</v>
+        <v>1.531421722758203</v>
       </c>
       <c r="G45">
-        <v>-4.392947535524893</v>
+        <v>-4.455287463932783</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-4.748046166020706</v>
       </c>
       <c r="E46">
-        <v>-22.49965725670766</v>
+        <v>-21.15001350583162</v>
       </c>
       <c r="F46">
-        <v>2.125667646504484</v>
+        <v>1.436611760038188</v>
       </c>
       <c r="G46">
-        <v>-4.482810350373406</v>
+        <v>-4.442238045790871</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-5.070956188739183</v>
       </c>
       <c r="E47">
-        <v>-21.37167778003308</v>
+        <v>-20.96114444039372</v>
       </c>
       <c r="F47">
-        <v>2.318524831754654</v>
+        <v>1.448694326975422</v>
       </c>
       <c r="G47">
-        <v>-4.29476026158007</v>
+        <v>-4.775918591057042</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-5.315183006702824</v>
       </c>
       <c r="E48">
-        <v>-20.57982428657783</v>
+        <v>-21.08777868754421</v>
       </c>
       <c r="F48">
-        <v>2.275542503958193</v>
+        <v>1.77802504183681</v>
       </c>
       <c r="G48">
-        <v>-4.248813316083165</v>
+        <v>-3.976124117163952</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-5.480884781288121</v>
       </c>
       <c r="E49">
-        <v>-20.70049000498622</v>
+        <v>-20.81287767290858</v>
       </c>
       <c r="F49">
-        <v>2.207982515320671</v>
+        <v>1.997366789689285</v>
       </c>
       <c r="G49">
-        <v>-4.533721784089749</v>
+        <v>-4.834586832539914</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-5.572616222794168</v>
       </c>
       <c r="E50">
-        <v>-20.15187896437898</v>
+        <v>-19.15974465098649</v>
       </c>
       <c r="F50">
-        <v>1.87604409987527</v>
+        <v>2.279203887878567</v>
       </c>
       <c r="G50">
-        <v>-4.450903751929365</v>
+        <v>-5.171387819509117</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-5.601143959174787</v>
       </c>
       <c r="E51">
-        <v>-20.08619797737173</v>
+        <v>-19.41207575116789</v>
       </c>
       <c r="F51">
-        <v>1.895868588559068</v>
+        <v>1.878602098415115</v>
       </c>
       <c r="G51">
-        <v>-4.387681174921984</v>
+        <v>-4.974406245630973</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-5.584191039775229</v>
       </c>
       <c r="E52">
-        <v>-18.72483000728983</v>
+        <v>-18.99448252055057</v>
       </c>
       <c r="F52">
-        <v>2.055387299316168</v>
+        <v>1.553371802197584</v>
       </c>
       <c r="G52">
-        <v>-4.300676304051748</v>
+        <v>-5.039331776627705</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-5.537847218979819</v>
       </c>
       <c r="E53">
-        <v>-18.86107820475861</v>
+        <v>-18.58572887119622</v>
       </c>
       <c r="F53">
-        <v>2.129271044706662</v>
+        <v>1.860901543752095</v>
       </c>
       <c r="G53">
-        <v>-4.883723125392598</v>
+        <v>-5.153344382153731</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-5.480540254999533</v>
       </c>
       <c r="E54">
-        <v>-18.46187510708644</v>
+        <v>-17.90260403866514</v>
       </c>
       <c r="F54">
-        <v>2.034895146505714</v>
+        <v>1.333655632279043</v>
       </c>
       <c r="G54">
-        <v>-4.571380363927497</v>
+        <v>-3.432251800021313</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-5.425860745891094</v>
       </c>
       <c r="E55">
-        <v>-17.73404065067763</v>
+        <v>-17.8580619683257</v>
       </c>
       <c r="F55">
-        <v>1.940699832398577</v>
+        <v>1.438203882186369</v>
       </c>
       <c r="G55">
-        <v>-4.24582740446407</v>
+        <v>-5.145508825069776</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-5.382216157546917</v>
       </c>
       <c r="E56">
-        <v>-18.33145505566553</v>
+        <v>-16.95261623286205</v>
       </c>
       <c r="F56">
-        <v>2.040050905220738</v>
+        <v>1.347292216463928</v>
       </c>
       <c r="G56">
-        <v>-4.106631423469307</v>
+        <v>-4.196973296665498</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-5.355356254847674</v>
       </c>
       <c r="E57">
-        <v>-17.49285865350311</v>
+        <v>-17.13016411328078</v>
       </c>
       <c r="F57">
-        <v>1.802304490412863</v>
+        <v>1.294003341441836</v>
       </c>
       <c r="G57">
-        <v>-4.8779219256755</v>
+        <v>-4.215978131937802</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-5.344348525950741</v>
       </c>
       <c r="E58">
-        <v>-16.76969758227022</v>
+        <v>-17.76776419661275</v>
       </c>
       <c r="F58">
-        <v>2.17971530606754</v>
+        <v>1.645014087969293</v>
       </c>
       <c r="G58">
-        <v>-4.456376829490519</v>
+        <v>-5.522065092453212</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-5.347227029660082</v>
       </c>
       <c r="E59">
-        <v>-15.59019312833636</v>
+        <v>-16.18011743731558</v>
       </c>
       <c r="F59">
-        <v>1.58572120601171</v>
+        <v>1.240790676220802</v>
       </c>
       <c r="G59">
-        <v>-5.140580430287491</v>
+        <v>-4.642231781060587</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-5.358871479589816</v>
       </c>
       <c r="E60">
-        <v>-16.50955939289959</v>
+        <v>-15.92585720720692</v>
       </c>
       <c r="F60">
-        <v>1.63044310535405</v>
+        <v>1.395750052792894</v>
       </c>
       <c r="G60">
-        <v>-5.03291698847899</v>
+        <v>-4.719625953983209</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-5.37068725969969</v>
       </c>
       <c r="E61">
-        <v>-15.80913578965921</v>
+        <v>-16.90442421247242</v>
       </c>
       <c r="F61">
-        <v>1.877140858316576</v>
+        <v>1.504428542570578</v>
       </c>
       <c r="G61">
-        <v>-5.094938638395615</v>
+        <v>-4.894072098191088</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-5.376170216468895</v>
       </c>
       <c r="E62">
-        <v>-15.64338911250447</v>
+        <v>-16.97026822454394</v>
       </c>
       <c r="F62">
-        <v>1.446903396650569</v>
+        <v>1.514798045718822</v>
       </c>
       <c r="G62">
-        <v>-4.82279412225527</v>
+        <v>-5.468246496435199</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-5.365514614665219</v>
       </c>
       <c r="E63">
-        <v>-15.49609143845697</v>
+        <v>-15.89371862717448</v>
       </c>
       <c r="F63">
-        <v>1.346831644187972</v>
+        <v>1.282300166775085</v>
       </c>
       <c r="G63">
-        <v>-5.503532753085468</v>
+        <v>-4.942424179091065</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-5.331609952662485</v>
       </c>
       <c r="E64">
-        <v>-14.56897695486662</v>
+        <v>-16.22531613638614</v>
       </c>
       <c r="F64">
-        <v>1.68668428179972</v>
+        <v>0.955108296547725</v>
       </c>
       <c r="G64">
-        <v>-5.40501407576314</v>
+        <v>-5.546198477022927</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-5.268108664845749</v>
       </c>
       <c r="E65">
-        <v>-15.16894994766886</v>
+        <v>-16.3590148029886</v>
       </c>
       <c r="F65">
-        <v>1.481471168369392</v>
+        <v>1.515155900436832</v>
       </c>
       <c r="G65">
-        <v>-5.637130970099819</v>
+        <v>-6.644262553112661</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-5.169455044277113</v>
       </c>
       <c r="E66">
-        <v>-14.4569696787609</v>
+        <v>-17.24739724839135</v>
       </c>
       <c r="F66">
-        <v>2.016893066108076</v>
+        <v>0.70346353345568</v>
       </c>
       <c r="G66">
-        <v>-6.110952488169874</v>
+        <v>-6.433280006840365</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-5.036381533656311</v>
       </c>
       <c r="E67">
-        <v>-15.01951936236375</v>
+        <v>-15.6044442360385</v>
       </c>
       <c r="F67">
-        <v>1.374686326474508</v>
+        <v>0.9186485336809076</v>
       </c>
       <c r="G67">
-        <v>-6.127411095512048</v>
+        <v>-7.15564093315212</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-4.869799657697326</v>
       </c>
       <c r="E68">
-        <v>-14.22428762729879</v>
+        <v>-16.53213383582783</v>
       </c>
       <c r="F68">
-        <v>1.229987108553491</v>
+        <v>0.8357985395225123</v>
       </c>
       <c r="G68">
-        <v>-6.947519612079661</v>
+        <v>-7.239239896043652</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-4.675971880716182</v>
       </c>
       <c r="E69">
-        <v>-15.5909810828137</v>
+        <v>-15.47240751939686</v>
       </c>
       <c r="F69">
-        <v>1.385383863114261</v>
+        <v>0.8172199154125249</v>
       </c>
       <c r="G69">
-        <v>-5.89375530826399</v>
+        <v>-7.445320297306137</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-4.461958035939512</v>
       </c>
       <c r="E70">
-        <v>-14.54856259404004</v>
+        <v>-15.27669592973336</v>
       </c>
       <c r="F70">
-        <v>1.580694672611523</v>
+        <v>0.09590574554641061</v>
       </c>
       <c r="G70">
-        <v>-6.426153193613252</v>
+        <v>-7.258628634238411</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-4.236830393221143</v>
       </c>
       <c r="E71">
-        <v>-15.53362795950655</v>
+        <v>-15.11828990894505</v>
       </c>
       <c r="F71">
-        <v>1.405024454234637</v>
+        <v>0.6635875834197174</v>
       </c>
       <c r="G71">
-        <v>-7.182428825963426</v>
+        <v>-7.910636889094111</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-4.01216133650439</v>
       </c>
       <c r="E72">
-        <v>-14.76688032594983</v>
+        <v>-16.50615850891983</v>
       </c>
       <c r="F72">
-        <v>1.394073437169628</v>
+        <v>0.7721534152306206</v>
       </c>
       <c r="G72">
-        <v>-6.789368014135984</v>
+        <v>-7.008589707744045</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-3.796503521898864</v>
       </c>
       <c r="E73">
-        <v>-14.86901552871883</v>
+        <v>-16.04661802356946</v>
       </c>
       <c r="F73">
-        <v>1.243853978876354</v>
+        <v>0.7264772366402559</v>
       </c>
       <c r="G73">
-        <v>-6.958580609956549</v>
+        <v>-7.181811956310251</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-3.601240296425953</v>
       </c>
       <c r="E74">
-        <v>-15.08573923777792</v>
+        <v>-16.29630902340439</v>
       </c>
       <c r="F74">
-        <v>1.218717998405806</v>
+        <v>0.7498057194378955</v>
       </c>
       <c r="G74">
-        <v>-6.129931073669701</v>
+        <v>-6.507196084909976</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-3.433007828850107</v>
       </c>
       <c r="E75">
-        <v>-15.07886501423427</v>
+        <v>-16.64104816418631</v>
       </c>
       <c r="F75">
-        <v>1.542056303475343</v>
+        <v>0.7073336659615593</v>
       </c>
       <c r="G75">
-        <v>-6.03043459232266</v>
+        <v>-6.734374740799691</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.29694579071091</v>
       </c>
       <c r="E76">
-        <v>-14.99254777117407</v>
+        <v>-15.99565004861313</v>
       </c>
       <c r="F76">
-        <v>1.016331274553831</v>
+        <v>0.219675432668296</v>
       </c>
       <c r="G76">
-        <v>-5.973689146673623</v>
+        <v>-6.876238354922283</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.195351406701191</v>
       </c>
       <c r="E77">
-        <v>-16.34453727158608</v>
+        <v>-17.95334106144708</v>
       </c>
       <c r="F77">
-        <v>1.272533715096079</v>
+        <v>0.2821442752482123</v>
       </c>
       <c r="G77">
-        <v>-6.371468355103546</v>
+        <v>-7.715594517157598</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.124987607740839</v>
       </c>
       <c r="E78">
-        <v>-15.44295885292498</v>
+        <v>-17.29378240765191</v>
       </c>
       <c r="F78">
-        <v>0.6668472091497335</v>
+        <v>0.2169790967721835</v>
       </c>
       <c r="G78">
-        <v>-5.684380560555823</v>
+        <v>-6.851018886016392</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.083210136637069</v>
       </c>
       <c r="E79">
-        <v>-16.10496288268428</v>
+        <v>-16.81858698765702</v>
       </c>
       <c r="F79">
-        <v>0.964611327392641</v>
+        <v>0.2677356526439176</v>
       </c>
       <c r="G79">
-        <v>-5.676374379950778</v>
+        <v>-7.332561118415819</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-3.061521953720825</v>
       </c>
       <c r="E80">
-        <v>-17.43691841408636</v>
+        <v>-17.68066352754922</v>
       </c>
       <c r="F80">
-        <v>1.010753048463379</v>
+        <v>0.2162650440709704</v>
       </c>
       <c r="G80">
-        <v>-5.979690500905847</v>
+        <v>-6.867339682053069</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-3.051619796675881</v>
       </c>
       <c r="E81">
-        <v>-17.12872858702034</v>
+        <v>-19.25233383054732</v>
       </c>
       <c r="F81">
-        <v>1.033292925493553</v>
+        <v>0.2334892874773805</v>
       </c>
       <c r="G81">
-        <v>-5.281348116409228</v>
+        <v>-6.61164721081178</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-3.043053700878295</v>
       </c>
       <c r="E82">
-        <v>-17.77256437906088</v>
+        <v>-17.37024569127143</v>
       </c>
       <c r="F82">
-        <v>0.8406378618896669</v>
+        <v>0.1943944879022578</v>
       </c>
       <c r="G82">
-        <v>-4.969878159878939</v>
+        <v>-6.126689226768971</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-3.025067001824267</v>
       </c>
       <c r="E83">
-        <v>-17.18627190623581</v>
+        <v>-20.10120534023315</v>
       </c>
       <c r="F83">
-        <v>0.6294356521370994</v>
+        <v>0.1636927068522998</v>
       </c>
       <c r="G83">
-        <v>-5.311676447283176</v>
+        <v>-5.454823019035511</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-2.989081905350564</v>
       </c>
       <c r="E84">
-        <v>-19.67233168086272</v>
+        <v>-19.81921726377551</v>
       </c>
       <c r="F84">
-        <v>0.8842861970779785</v>
+        <v>0.4408337902351108</v>
       </c>
       <c r="G84">
-        <v>-5.225147353539059</v>
+        <v>-5.304520103062027</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-2.926649882437849</v>
       </c>
       <c r="E85">
-        <v>-20.37866494268311</v>
+        <v>-21.05395098670691</v>
       </c>
       <c r="F85">
-        <v>0.799065415412771</v>
+        <v>0.3926045833093179</v>
       </c>
       <c r="G85">
-        <v>-4.151384004318573</v>
+        <v>-5.338172311375692</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-2.836682433925141</v>
       </c>
       <c r="E86">
-        <v>-20.4552323812048</v>
+        <v>-22.34707938196722</v>
       </c>
       <c r="F86">
-        <v>1.140341188222528</v>
+        <v>-0.111499228031724</v>
       </c>
       <c r="G86">
-        <v>-4.239668551596993</v>
+        <v>-5.287054160701103</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-2.721223516412873</v>
       </c>
       <c r="E87">
-        <v>-21.72455458860679</v>
+        <v>-23.66456191044078</v>
       </c>
       <c r="F87">
-        <v>0.8633135911739006</v>
+        <v>0.3425571099343802</v>
       </c>
       <c r="G87">
-        <v>-4.136287103923568</v>
+        <v>-5.226453279719718</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-2.58715028571677</v>
       </c>
       <c r="E88">
-        <v>-22.59825119280266</v>
+        <v>-25.19578388360237</v>
       </c>
       <c r="F88">
-        <v>0.7993238660424444</v>
+        <v>0.3661531554031241</v>
       </c>
       <c r="G88">
-        <v>-4.376108306481822</v>
+        <v>-4.55830469601311</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-2.444189467984657</v>
       </c>
       <c r="E89">
-        <v>-24.80542489566718</v>
+        <v>-25.95129637314606</v>
       </c>
       <c r="F89">
-        <v>0.6511960354412396</v>
+        <v>0.3644119271224396</v>
       </c>
       <c r="G89">
-        <v>-3.933612610639787</v>
+        <v>-5.032431367688193</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-2.303542600070942</v>
       </c>
       <c r="E90">
-        <v>-24.85807746295437</v>
+        <v>-26.34836203108662</v>
       </c>
       <c r="F90">
-        <v>1.267010161254212</v>
+        <v>0.4127363962995543</v>
       </c>
       <c r="G90">
-        <v>-4.16629059386313</v>
+        <v>-3.917439469573284</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-2.179505336391511</v>
       </c>
       <c r="E91">
-        <v>-27.41076920413013</v>
+        <v>-28.05187432634404</v>
       </c>
       <c r="F91">
-        <v>0.7722743568714293</v>
+        <v>0.138212125542187</v>
       </c>
       <c r="G91">
-        <v>-3.697689499294152</v>
+        <v>-5.594829461755458</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-2.08490161624455</v>
       </c>
       <c r="E92">
-        <v>-28.36506358871452</v>
+        <v>-28.89626717523628</v>
       </c>
       <c r="F92">
-        <v>0.7736693275777438</v>
+        <v>0.3025502778487753</v>
       </c>
       <c r="G92">
-        <v>-4.189022896826963</v>
+        <v>-4.404700871150824</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-2.033127166859688</v>
       </c>
       <c r="E93">
-        <v>-29.74535378743746</v>
+        <v>-29.51661150836202</v>
       </c>
       <c r="F93">
-        <v>0.8446902352241621</v>
+        <v>0.1785295954038417</v>
       </c>
       <c r="G93">
-        <v>-4.053518290086575</v>
+        <v>-4.856055865203361</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-2.032609724886673</v>
       </c>
       <c r="E94">
-        <v>-32.01992476895815</v>
+        <v>-32.32347291016629</v>
       </c>
       <c r="F94">
-        <v>0.8232438031656829</v>
+        <v>-0.05214007668191704</v>
       </c>
       <c r="G94">
-        <v>-3.578253034530364</v>
+        <v>-4.342305161976423</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-2.089783736374555</v>
       </c>
       <c r="E95">
-        <v>-33.77604434676267</v>
+        <v>-35.71152093035199</v>
       </c>
       <c r="F95">
-        <v>0.5785159078870138</v>
+        <v>-0.4626267743629757</v>
       </c>
       <c r="G95">
-        <v>-3.692222984176117</v>
+        <v>-5.760068498267534</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-2.208352097973385</v>
       </c>
       <c r="E96">
-        <v>-35.99839975873791</v>
+        <v>-37.34574304481805</v>
       </c>
       <c r="F96">
-        <v>0.5114123496884342</v>
+        <v>-0.08446380110655655</v>
       </c>
       <c r="G96">
-        <v>-3.60912604818318</v>
+        <v>-5.462474827712136</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-2.380723572121556</v>
       </c>
       <c r="E97">
-        <v>-38.40696828614556</v>
+        <v>-38.41297304267973</v>
       </c>
       <c r="F97">
-        <v>0.4973764924153994</v>
+        <v>-0.2988925018930282</v>
       </c>
       <c r="G97">
-        <v>-3.572130275100441</v>
+        <v>-5.392109031369844</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-2.606585955452847</v>
       </c>
       <c r="E98">
-        <v>-40.14179950764003</v>
+        <v>-41.13378664562726</v>
       </c>
       <c r="F98">
-        <v>0.3287382849208789</v>
+        <v>0.1498390904078808</v>
       </c>
       <c r="G98">
-        <v>-4.282334275534453</v>
+        <v>-4.740028589639836</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-2.862250858218674</v>
       </c>
       <c r="E99">
-        <v>-42.18587569064429</v>
+        <v>-45.38873176628631</v>
       </c>
       <c r="F99">
-        <v>0.1752898504914928</v>
+        <v>-0.6891015939209577</v>
       </c>
       <c r="G99">
-        <v>-4.793325471429897</v>
+        <v>-5.350027364869965</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-3.150995228263399</v>
       </c>
       <c r="E100">
-        <v>-44.59465705633031</v>
+        <v>-45.73184518489948</v>
       </c>
       <c r="F100">
-        <v>0.2932377715065033</v>
+        <v>-0.5053398827535266</v>
       </c>
       <c r="G100">
-        <v>-4.760936533416618</v>
+        <v>-5.463177009125857</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-3.431453751101329</v>
       </c>
       <c r="E101">
-        <v>-47.53458540261298</v>
+        <v>-48.81635978141755</v>
       </c>
       <c r="F101">
-        <v>0.2543111305141489</v>
+        <v>-0.8437486759821946</v>
       </c>
       <c r="G101">
-        <v>-4.900089858531109</v>
+        <v>-6.084000534280595</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-3.738490609091741</v>
       </c>
       <c r="E102">
-        <v>-50.35850783024115</v>
+        <v>-52.04836677636545</v>
       </c>
       <c r="F102">
-        <v>-0.08967588880497103</v>
+        <v>-1.278177676706367</v>
       </c>
       <c r="G102">
-        <v>-5.534149831456646</v>
+        <v>-5.644126534464555</v>
       </c>
     </row>
   </sheetData>
